--- a/monitoring_forms/043_vessel_impact_monitoring_log_form--monitoring_forms.xlsx
+++ b/monitoring_forms/043_vessel_impact_monitoring_log_form--monitoring_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -937,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'marina'}</t>
+          <t>marina</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'marina'}</t>
+          <t>marina</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'sail'}</t>
+          <t>sail</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'sail'}</t>
+          <t>sail</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'grounding'}</t>
+          <t>grounding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'grounding'}</t>
+          <t>grounding</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'major'}</t>
+          <t>major</t>
         </is>
       </c>
     </row>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'major'}</t>
+          <t>major</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'major'}</t>
+          <t>major</t>
         </is>
       </c>
     </row>
@@ -1220,17 +1220,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>severity_choices</t>
+          <t>assigned_to_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>minor</t>
+          <t>marina</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>minor</t>
+          <t>marina</t>
         </is>
       </c>
     </row>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'marina'}</t>
+          <t>port</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'marina'}</t>
+          <t>port</t>
         </is>
       </c>
     </row>
@@ -1259,29 +1259,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>boat</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'new'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'new'}</t>
+          <t>ongoing</t>
         </is>
       </c>
     </row>
@@ -1310,29 +1310,29 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>closed</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'new'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'new'}</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
@@ -1361,29 +1361,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>follow_up_status_choices</t>
+          <t>follow_up_assigned_to_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>marina</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>marina</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'name':_'marina'}</t>
+          <t>port</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'name': 'marina'}</t>
+          <t>port</t>
         </is>
       </c>
     </row>
@@ -1412,29 +1412,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>boat</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>port</t>
+          <t>boat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>follow_up_assigned_to_choices</t>
+          <t>follow_up_status_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>boat</t>
+          <t>new</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'name':_'new'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'name': 'new'}</t>
+          <t>in progress</t>
         </is>
       </c>
     </row>
@@ -1463,27 +1463,10 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
-        <is>
-          <t>in_progress</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>follow_up_status_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>completed</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
         <is>
           <t>completed</t>
         </is>
